--- a/backend/mou_data.xlsx
+++ b/backend/mou_data.xlsx
@@ -397,95 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Institute</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Duration</v>
-      </c>
-      <c r="C1" t="str">
-        <v>FacultyName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>FacultyDetails</v>
-      </c>
-      <c r="E1" t="str">
-        <v>AcademicYear</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Purpose</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Outcomes</v>
-      </c>
-      <c r="H1" t="str">
-        <v>SignedDoc</v>
-      </c>
-      <c r="I1" t="str">
-        <v>AddedDate</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>SNU</v>
-      </c>
-      <c r="B2" t="str">
-        <v>4</v>
-      </c>
-      <c r="C2" t="str">
-        <v>MYSELF</v>
-      </c>
-      <c r="D2" t="str">
-        <v>CSE</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2026</v>
-      </c>
-      <c r="F2" t="str">
-        <v>STUDY</v>
-      </c>
-      <c r="G2" t="str">
-        <v>PUBLISHED</v>
-      </c>
-      <c r="H2" t="str">
-        <v>1744733129227-SOP.docx</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>SSN</v>
-      </c>
-      <c r="B3" t="str">
-        <v>1</v>
-      </c>
-      <c r="C3" t="str">
-        <v>MYSELF</v>
-      </c>
-      <c r="D3" t="str">
-        <v>CSE</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026</v>
-      </c>
-      <c r="F3" t="str">
-        <v>STUDY</v>
-      </c>
-      <c r="G3" t="str">
-        <v>PUBLISHED</v>
-      </c>
-      <c r="H3" t="str">
-        <v>1744735354583-Lab Record Wrapper &amp; Index_20211027_0001.pdf</v>
-      </c>
-      <c r="I3" t="str">
-        <v>2025-04-15T16:42:34.572Z</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>